--- a/src/Excelsior.Tests/TemplateSheetTests.EnumDropdownAutoDerived.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.EnumDropdownAutoDerived.verified.xlsx
@@ -41,6 +41,15 @@
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
   </cellXfs>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -65,8 +74,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:B1"/>
+  <conditionalFormatting sqref="B2:B51">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B51">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="B2:B51">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TemplateSheetTests.EnumDropdownAutoDerived.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.EnumDropdownAutoDerived.verified.xlsx
@@ -80,7 +80,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="B2:B51">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="B2:B51">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TemplateSheetTests.EnumDropdownAutoDerived.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.EnumDropdownAutoDerived.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -85,4 +85,13 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Employees">
+    <column index="1" property="Name"/>
+    <column index="2" property="Status"/>
+  </sheet>
+</columnMetadata>
 </file>